--- a/Unity/Assets/Config/Excel/FuntionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/FuntionConfig.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>#</t>
   </si>
@@ -181,6 +181,9 @@
   </si>
   <si>
     <t>WindowID_MedalExchange</t>
+  </si>
+  <si>
+    <t>巧儿</t>
   </si>
 </sst>
 </file>
@@ -1346,7 +1349,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1"/>
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C7" s="2">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+    </row>
     <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>

--- a/Unity/Assets/Config/Excel/FuntionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/FuntionConfig.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>#</t>
   </si>
@@ -184,6 +184,9 @@
   </si>
   <si>
     <t>巧儿</t>
+  </si>
+  <si>
+    <t>WindowID_NecklaceRefine</t>
   </si>
 </sst>
 </file>
@@ -362,12 +365,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1357,7 +1360,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>

--- a/Unity/Assets/Config/Excel/FuntionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/FuntionConfig.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>#</t>
   </si>
@@ -187,6 +187,12 @@
   </si>
   <si>
     <t>WindowID_NecklaceRefine</t>
+  </si>
+  <si>
+    <t>鉴定家</t>
+  </si>
+  <si>
+    <t>WindowID_EquipIdentify</t>
   </si>
 </sst>
 </file>
@@ -365,12 +371,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1375,17 +1381,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C8" s="2">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
       <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="I8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
       <c r="C9" s="2"/>

--- a/Unity/Assets/Config/Excel/FuntionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/FuntionConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="22110" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="FunctionOpenProto" sheetId="1" r:id="rId1"/>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>#</t>
   </si>
@@ -193,6 +193,12 @@
   </si>
   <si>
     <t>WindowID_EquipIdentify</t>
+  </si>
+  <si>
+    <t>珠宝匠</t>
+  </si>
+  <si>
+    <t>WindowID_Gem</t>
   </si>
 </sst>
 </file>
@@ -1381,7 +1387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+    <row r="8" s="2" customFormat="1" ht="21" customHeight="1" spans="3:12">
       <c r="C8" s="2">
         <v>1003</v>
       </c>
@@ -1405,17 +1411,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+    <row r="9" s="2" customFormat="1" ht="21" customHeight="1" spans="3:12">
+      <c r="C9" s="2">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="I9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
       <c r="C10" s="2"/>

--- a/Unity/Assets/Config/Excel/FuntionConfig.xlsx
+++ b/Unity/Assets/Config/Excel/FuntionConfig.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="32">
   <si>
     <t>#</t>
   </si>
@@ -199,6 +199,12 @@
   </si>
   <si>
     <t>WindowID_Gem</t>
+  </si>
+  <si>
+    <t>锻造师</t>
+  </si>
+  <si>
+    <t>WindowID_EquipStrength</t>
   </si>
 </sst>
 </file>
@@ -1435,17 +1441,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
+    <row r="10" s="2" customFormat="1" ht="21" customHeight="1" spans="3:12">
+      <c r="C10" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="I10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J10" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" ht="20.1" customHeight="1"/>
     <row r="12" ht="20.1" customHeight="1"/>
